--- a/reports/devops-juniors-israel-2026-W39.xlsx
+++ b/reports/devops-juniors-israel-2026-W39.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-21T12:41:34</t>
+    <t xml:space="preserve">2026-09-22T11:27:56</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
-    <t xml:space="preserve">Associate Development Operations Engineer</t>
+    <t xml:space="preserve">Development Operations Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Clarivate</t>
@@ -162,7 +162,7 @@
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/associate-development-operations-engineer-at-clarivate-4467992253</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-16</t>
@@ -525,184 +525,175 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Engineer II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWeber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uluberia-II,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
@@ -920,7 +911,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -936,7 +927,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -944,7 +935,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>456</v>
+        <v>446</v>
       </c>
     </row>
     <row r="10">
@@ -1026,7 +1017,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1084,7 +1075,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -1933,25 +1924,25 @@
         <v>171</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2004,7 +1995,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2019,22 +2010,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2">
@@ -2057,7 +2048,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2069,7 +2060,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -2092,7 +2083,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2104,7 +2095,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -2127,7 +2118,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2139,7 +2130,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -2162,7 +2153,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2174,7 +2165,7 @@
         <v>56</v>
       </c>
       <c r="K5" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -2197,7 +2188,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2209,7 +2200,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -2232,7 +2223,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2244,7 +2235,7 @@
         <v>56</v>
       </c>
       <c r="K7" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -2267,7 +2258,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2279,7 +2270,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -2302,7 +2293,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2314,7 +2305,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -2337,7 +2328,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2349,7 +2340,7 @@
         <v>50</v>
       </c>
       <c r="K10" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -2372,7 +2363,7 @@
         <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2384,7 +2375,7 @@
         <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -2407,7 +2398,7 @@
         <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2419,7 +2410,7 @@
         <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -2442,7 +2433,7 @@
         <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2454,7 +2445,7 @@
         <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -2477,7 +2468,7 @@
         <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2489,7 +2480,7 @@
         <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -2512,7 +2503,7 @@
         <v>120</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2524,7 +2515,7 @@
         <v>56</v>
       </c>
       <c r="K15" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -2547,7 +2538,7 @@
         <v>124</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
@@ -2559,7 +2550,7 @@
         <v>126</v>
       </c>
       <c r="K16" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17">
@@ -2582,7 +2573,7 @@
         <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2594,7 +2585,7 @@
         <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -2617,7 +2608,7 @@
         <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
@@ -2629,7 +2620,7 @@
         <v>56</v>
       </c>
       <c r="K18" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
@@ -2652,7 +2643,7 @@
         <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
@@ -2664,7 +2655,7 @@
         <v>140</v>
       </c>
       <c r="K19" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -2687,7 +2678,7 @@
         <v>144</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
@@ -2699,7 +2690,7 @@
         <v>146</v>
       </c>
       <c r="K20" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -2722,7 +2713,7 @@
         <v>150</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
@@ -2734,7 +2725,7 @@
         <v>152</v>
       </c>
       <c r="K21" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -2757,7 +2748,7 @@
         <v>154</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
@@ -2769,7 +2760,7 @@
         <v>156</v>
       </c>
       <c r="K22" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -2792,7 +2783,7 @@
         <v>159</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
@@ -2804,7 +2795,7 @@
         <v>161</v>
       </c>
       <c r="K23" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24">
@@ -2827,7 +2818,7 @@
         <v>164</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
@@ -2839,7 +2830,7 @@
         <v>166</v>
       </c>
       <c r="K24" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -2862,7 +2853,7 @@
         <v>168</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
@@ -2874,7 +2865,7 @@
         <v>116</v>
       </c>
       <c r="K25" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -2885,66 +2876,66 @@
         <v>171</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E26" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="K26" s="3">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="3">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D27" s="3" t="s">
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="3">
         <v>27</v>
-      </c>
-      <c r="E27" s="3">
-        <v>10</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="K27" s="3">
-        <v>28</v>
       </c>
     </row>
     <row r="28">
@@ -2952,48 +2943,48 @@
         <v>185</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="3">
+        <v>8</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="3">
-        <v>9</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>110</v>
       </c>
       <c r="K28" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
         <v>8</v>
@@ -3002,7 +2993,7 @@
         <v>190</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
@@ -3011,126 +3002,124 @@
         <v>191</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="K29" s="3">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>90</v>
+        <v>195</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K30" s="3">
-        <v>6</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K31" s="3">
-        <v>81</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>206</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K32" s="3">
-        <v>11</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3140,56 +3129,23 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K33" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="3">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="K34" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K34"/>
+  <autoFilter ref="A1:K33"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3223,7 +3179,6 @@
     <hyperlink ref="I31" r:id="rId30"/>
     <hyperlink ref="I32" r:id="rId31"/>
     <hyperlink ref="I33" r:id="rId32"/>
-    <hyperlink ref="I34" r:id="rId33"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3238,178 +3193,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B2" s="3">
         <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B3" s="3">
         <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B4" s="3">
         <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -3429,10 +3384,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2">
@@ -3440,10 +3395,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3">
@@ -3454,7 +3409,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4">
@@ -3465,7 +3420,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5">
@@ -3476,7 +3431,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6">
@@ -3487,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7">
@@ -3498,7 +3453,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -3519,13 +3474,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -3536,7 +3491,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3545,10 +3500,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3560,7 +3515,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W39.xlsx
+++ b/reports/devops-juniors-israel-2026-W39.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="255">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-22T11:27:56</t>
+    <t xml:space="preserve">2026-09-23T11:25:20</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -168,6 +168,24 @@
     <t xml:space="preserve">2026-09-16</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
     <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
   </si>
   <si>
@@ -186,24 +204,6 @@
     <t xml:space="preserve">2026-08-20</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
@@ -438,24 +438,6 @@
     <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
   </si>
   <si>
@@ -525,6 +507,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
   </si>
   <si>
@@ -684,18 +678,15 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
@@ -741,16 +732,16 @@
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -927,7 +918,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -935,7 +926,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>446</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10">
@@ -1017,7 +1008,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -1033,7 +1024,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1191,7 +1182,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1223,7 +1214,7 @@
         <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1252,7 +1243,7 @@
         <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
@@ -1270,7 +1261,7 @@
         <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -1284,7 +1275,7 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
@@ -1334,7 +1325,7 @@
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -1380,7 +1371,7 @@
         <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1590,7 +1581,7 @@
         <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1595,7 @@
         <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
@@ -1668,7 +1659,7 @@
         <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -1686,7 +1677,7 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -1735,10 +1726,10 @@
         <v>143</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>144</v>
@@ -1758,13 +1749,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="D21" s="3" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -1773,16 +1764,16 @@
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="22">
@@ -1790,13 +1781,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -1805,16 +1796,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="23">
@@ -1822,31 +1813,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="3">
+        <v>23</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="3">
-        <v>24</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="24">
@@ -1854,31 +1845,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="3">
+        <v>12</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="3">
-        <v>23</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>166</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
@@ -1886,13 +1877,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -1901,16 +1892,16 @@
         <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26">
@@ -1918,13 +1909,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1933,16 +1924,16 @@
         <v>10</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -1995,7 +1986,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2010,22 +2001,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
@@ -2048,7 +2039,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2060,7 +2051,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2074,7 +2065,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2083,7 +2074,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2095,7 +2086,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -2109,7 +2100,7 @@
         <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -2118,7 +2109,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2130,7 +2121,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -2141,7 +2132,7 @@
         <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
@@ -2153,7 +2144,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2162,10 +2153,10 @@
         <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -2176,7 +2167,7 @@
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
@@ -2188,7 +2179,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2200,7 +2191,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -2223,7 +2214,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2232,10 +2223,10 @@
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K7" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
@@ -2258,7 +2249,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2270,7 +2261,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -2281,7 +2272,7 @@
         <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
@@ -2293,7 +2284,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2305,7 +2296,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -2328,7 +2319,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2340,7 +2331,7 @@
         <v>50</v>
       </c>
       <c r="K10" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -2363,7 +2354,7 @@
         <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2375,7 +2366,7 @@
         <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -2398,7 +2389,7 @@
         <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2410,7 +2401,7 @@
         <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -2433,7 +2424,7 @@
         <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2445,7 +2436,7 @@
         <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -2468,7 +2459,7 @@
         <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2480,7 +2471,7 @@
         <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -2503,7 +2494,7 @@
         <v>120</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2512,10 +2503,10 @@
         <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K15" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2526,7 +2517,7 @@
         <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
@@ -2538,7 +2529,7 @@
         <v>124</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
@@ -2550,7 +2541,7 @@
         <v>126</v>
       </c>
       <c r="K16" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -2573,7 +2564,7 @@
         <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2585,7 +2576,7 @@
         <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -2596,7 +2587,7 @@
         <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
@@ -2608,7 +2599,7 @@
         <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
@@ -2617,10 +2608,10 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K18" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
@@ -2643,7 +2634,7 @@
         <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
@@ -2655,7 +2646,7 @@
         <v>140</v>
       </c>
       <c r="K19" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -2669,16 +2660,16 @@
         <v>143</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>144</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
@@ -2690,18 +2681,18 @@
         <v>146</v>
       </c>
       <c r="K20" s="3">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="C21" s="3" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
@@ -2710,33 +2701,33 @@
         <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="K21" s="3">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -2745,103 +2736,103 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="K22" s="3">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="3">
+        <v>23</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>24</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="K23" s="3">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>12</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="3">
-        <v>23</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>166</v>
+        <v>116</v>
       </c>
       <c r="K24" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
@@ -2850,33 +2841,33 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="K25" s="3">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>27</v>
@@ -2885,33 +2876,33 @@
         <v>10</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K26" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>30</v>
@@ -2920,33 +2911,33 @@
         <v>9</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>110</v>
       </c>
       <c r="K27" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>26</v>
@@ -2955,30 +2946,30 @@
         <v>8</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>110</v>
       </c>
       <c r="K28" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>90</v>
@@ -2990,33 +2981,33 @@
         <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="K29" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
@@ -3025,33 +3016,33 @@
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K30" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3060,33 +3051,33 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K31" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
@@ -3096,30 +3087,30 @@
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K32" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3129,19 +3120,19 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K33" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3186,185 +3177,185 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3384,10 +3375,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2">
@@ -3395,10 +3386,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3">
@@ -3409,7 +3400,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4">
@@ -3417,10 +3408,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5">
@@ -3431,7 +3422,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6">
@@ -3442,7 +3433,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7">
@@ -3453,7 +3444,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -3474,13 +3465,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2">
@@ -3491,7 +3482,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3503,7 +3494,7 @@
         <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3515,7 +3506,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W39.xlsx
+++ b/reports/devops-juniors-israel-2026-W39.xlsx
@@ -5,15 +5,16 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="🪜 Top Picks" sheetId="2" r:id="rId2"/>
     <sheet name="All Matches" sheetId="3" r:id="rId3"/>
-    <sheet name="Stack Demand" sheetId="4" r:id="rId4"/>
-    <sheet name="Buckets" sheetId="5" r:id="rId5"/>
-    <sheet name="Diagnostics" sheetId="6" r:id="rId6"/>
+    <sheet name="🔥 New Today" sheetId="4" r:id="rId4"/>
+    <sheet name="Stack Demand" sheetId="5" r:id="rId5"/>
+    <sheet name="Buckets" sheetId="6" r:id="rId6"/>
+    <sheet name="Diagnostics" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -30,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23T11:25:20</t>
+    <t xml:space="preserve">2026-09-24T11:37:25</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -99,15 +100,15 @@
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior DevOps</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -279,201 +280,195 @@
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Analyst | Splunk &amp; Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-splunk-infrastructure-at-confidential-careers-4465957826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator 7992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
   </si>
   <si>
@@ -534,6 +529,18 @@
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -552,18 +559,6 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
   </si>
   <si>
@@ -606,6 +601,18 @@
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
     <t xml:space="preserve">Operations Engineer II</t>
   </si>
   <si>
@@ -663,30 +670,27 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
@@ -702,16 +706,22 @@
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -720,12 +730,6 @@
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
@@ -759,13 +763,13 @@
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -910,7 +914,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -918,7 +922,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -926,7 +930,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10">
@@ -1008,7 +1012,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -1024,7 +1028,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1032,7 +1036,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1095,7 +1099,7 @@
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -1182,7 +1186,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1406,10 +1410,10 @@
         <v>90</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>91</v>
@@ -1421,7 +1425,7 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -1429,13 +1433,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1444,16 +1448,16 @@
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -1461,31 +1465,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1493,31 +1497,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -1525,31 +1529,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15">
@@ -1557,13 +1561,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
@@ -1572,13 +1576,13 @@
         <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>62</v>
@@ -1589,10 +1593,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>53</v>
@@ -1604,16 +1608,16 @@
         <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
@@ -1621,31 +1625,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>128</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -1653,31 +1657,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3">
+        <v>27</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>28</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -1691,7 +1695,7 @@
         <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1700,16 +1704,16 @@
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20">
@@ -1717,13 +1721,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -1732,16 +1736,16 @@
         <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21">
@@ -1749,13 +1753,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -1764,16 +1768,16 @@
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22">
@@ -1781,31 +1785,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F22" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23">
@@ -1813,31 +1817,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24">
@@ -1845,13 +1849,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
@@ -1860,16 +1864,16 @@
         <v>12</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25">
@@ -1877,31 +1881,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26">
@@ -1909,31 +1913,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F26" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>172</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1973,7 +1977,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -1986,7 +1990,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2001,22 +2005,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2">
@@ -2039,7 +2043,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2051,7 +2055,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2065,7 +2069,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2074,7 +2078,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2086,7 +2090,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -2109,7 +2113,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2121,7 +2125,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -2144,7 +2148,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2156,7 +2160,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -2179,7 +2183,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2191,7 +2195,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -2214,7 +2218,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2226,7 +2230,7 @@
         <v>62</v>
       </c>
       <c r="K7" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -2249,7 +2253,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2261,7 +2265,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -2284,7 +2288,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2296,7 +2300,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -2310,16 +2314,16 @@
         <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2328,21 +2332,21 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>27</v>
@@ -2351,138 +2355,138 @@
         <v>47</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E12" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K14" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
@@ -2491,30 +2495,30 @@
         <v>39</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>62</v>
       </c>
       <c r="K15" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>53</v>
@@ -2526,92 +2530,92 @@
         <v>36</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K16" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="K17" s="3">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>28</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K18" s="3">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
@@ -2622,7 +2626,7 @@
         <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>27</v>
@@ -2631,33 +2635,33 @@
         <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K19" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
@@ -2666,33 +2670,33 @@
         <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K20" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
@@ -2701,103 +2705,103 @@
         <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K21" s="3">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E22" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K22" s="3">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
+        <v>12</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K23" s="3">
         <v>23</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="K23" s="3">
-        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
@@ -2806,243 +2810,243 @@
         <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="K24" s="3">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="K25" s="3">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E26" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>172</v>
+        <v>105</v>
       </c>
       <c r="K26" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="3">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" s="3">
-        <v>9</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="K27" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>58</v>
+        <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>59</v>
+        <v>150</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
         <v>8</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="K28" s="3">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="K29" s="3">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E30" s="3">
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="K30" s="3">
-        <v>83</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3051,33 +3055,33 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K31" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
@@ -3087,30 +3091,30 @@
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K32" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3120,19 +3124,19 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K33" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3177,6 +3181,72 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3">
+        <v>40</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G2"/>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1"/>
+  </hyperlinks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
@@ -3184,185 +3254,185 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B3" s="3">
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -3375,10 +3445,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2">
@@ -3386,10 +3456,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3">
@@ -3400,7 +3470,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4">
@@ -3408,10 +3478,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5">
@@ -3419,10 +3489,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6">
@@ -3433,7 +3503,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7">
@@ -3444,14 +3514,14 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3465,13 +3535,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2">
@@ -3482,7 +3552,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3494,7 +3564,7 @@
         <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3506,7 +3576,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W39.xlsx
+++ b/reports/devops-juniors-israel-2026-W39.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="255">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24T11:37:25</t>
+    <t xml:space="preserve">2026-09-25T11:43:55</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -460,42 +460,27 @@
     <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
     <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
@@ -541,6 +526,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -559,15 +553,6 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Engineer- Student Position</t>
   </si>
   <si>
@@ -601,15 +586,27 @@
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC 243952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-243952-at-experis-4469770052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Power Control System Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">SolarEdge Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
   </si>
   <si>
@@ -742,10 +739,10 @@
     <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -922,7 +919,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -930,7 +927,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10">
@@ -1759,25 +1756,25 @@
         <v>149</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="3">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="3">
-        <v>24</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="22">
@@ -1785,31 +1782,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="3">
+        <v>12</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="3">
-        <v>23</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23">
@@ -1817,13 +1814,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -1832,16 +1829,16 @@
         <v>12</v>
       </c>
       <c r="G23" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24">
@@ -1849,31 +1846,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="25">
@@ -1887,25 +1884,25 @@
         <v>167</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" s="3">
+        <v>9</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="3">
-        <v>10</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="H25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>170</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26">
@@ -1913,28 +1910,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="3">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F26" s="3">
-        <v>9</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>105</v>
@@ -1990,7 +1987,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2005,22 +2002,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
@@ -2043,7 +2040,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2055,7 +2052,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2078,7 +2075,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2090,7 +2087,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -2113,7 +2110,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2125,7 +2122,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -2148,7 +2145,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2160,7 +2157,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -2183,7 +2180,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2195,7 +2192,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -2218,7 +2215,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2230,7 +2227,7 @@
         <v>62</v>
       </c>
       <c r="K7" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -2253,7 +2250,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2265,7 +2262,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -2288,7 +2285,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2300,7 +2297,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -2323,7 +2320,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2335,7 +2332,7 @@
         <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -2358,7 +2355,7 @@
         <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2370,7 +2367,7 @@
         <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -2393,7 +2390,7 @@
         <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2405,7 +2402,7 @@
         <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -2428,7 +2425,7 @@
         <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2440,7 +2437,7 @@
         <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -2463,7 +2460,7 @@
         <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2475,7 +2472,7 @@
         <v>117</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2498,7 +2495,7 @@
         <v>121</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2510,7 +2507,7 @@
         <v>62</v>
       </c>
       <c r="K15" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2533,7 +2530,7 @@
         <v>125</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
@@ -2545,7 +2542,7 @@
         <v>127</v>
       </c>
       <c r="K16" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -2568,7 +2565,7 @@
         <v>129</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2580,7 +2577,7 @@
         <v>62</v>
       </c>
       <c r="K17" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -2603,7 +2600,7 @@
         <v>133</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
@@ -2615,7 +2612,7 @@
         <v>135</v>
       </c>
       <c r="K18" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -2638,7 +2635,7 @@
         <v>139</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
@@ -2650,7 +2647,7 @@
         <v>141</v>
       </c>
       <c r="K19" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -2673,7 +2670,7 @@
         <v>145</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
@@ -2685,7 +2682,7 @@
         <v>147</v>
       </c>
       <c r="K20" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -2696,77 +2693,77 @@
         <v>149</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="3">
+        <v>23</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>24</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="K21" s="3">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="D22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3">
+        <v>12</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="3">
-        <v>23</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="K22" s="3">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -2775,57 +2772,57 @@
         <v>12</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="K23" s="3">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="K24" s="3">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
@@ -2836,101 +2833,101 @@
         <v>167</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="3">
+        <v>9</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="3">
-        <v>10</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="G25" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="K25" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="3">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="3">
-        <v>9</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>105</v>
       </c>
       <c r="K26" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>58</v>
+        <v>180</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
         <v>8</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K27" s="3">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -2941,45 +2938,45 @@
         <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K28" s="3">
-        <v>9</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
         <v>4</v>
@@ -2988,10 +2985,10 @@
         <v>192</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>193</v>
@@ -3000,7 +2997,7 @@
         <v>194</v>
       </c>
       <c r="K29" s="3">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3020,33 +3017,33 @@
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>71</v>
       </c>
       <c r="K30" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3055,33 +3052,33 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I31" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="K31" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
@@ -3091,30 +3088,30 @@
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="K32" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3124,19 +3121,19 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="K33" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -3181,11 +3178,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3204,10 +3201,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3215,25 +3212,25 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>115</v>
+        <v>192</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>116</v>
+        <v>193</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>117</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -3254,178 +3251,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B3" s="3">
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" s="3">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="B5" s="3">
-        <v>14</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3445,10 +3442,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="2">
@@ -3459,7 +3456,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3">
@@ -3470,7 +3467,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4">
@@ -3481,7 +3478,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5">
@@ -3492,7 +3489,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6">
@@ -3503,7 +3500,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7">
@@ -3514,7 +3511,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -3535,13 +3532,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="2">
@@ -3552,7 +3549,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3564,7 +3561,7 @@
         <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3576,7 +3573,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W39.xlsx
+++ b/reports/devops-juniors-israel-2026-W39.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25T11:43:55</t>
+    <t xml:space="preserve">2026-09-27T11:56:19</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -409,6 +409,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4472436545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27</t>
+  </si>
+  <si>
     <t xml:space="preserve">Support Engineer</t>
   </si>
   <si>
@@ -424,24 +439,6 @@
     <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
   </si>
   <si>
@@ -460,6 +457,18 @@
     <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
   </si>
   <si>
@@ -487,193 +496,187 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC 243952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-243952-at-experis-4469770052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC 243952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-243952-at-experis-4469770052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Engineer II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWeber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uluberia-II,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
@@ -683,9 +686,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
@@ -919,7 +919,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -927,7 +927,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>437</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10">
@@ -1009,7 +1009,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1025,7 +1025,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1660,13 +1660,13 @@
         <v>132</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>133</v>
@@ -1692,7 +1692,7 @@
         <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1701,16 +1701,16 @@
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="20">
@@ -1718,13 +1718,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -1733,16 +1733,16 @@
         <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="21">
@@ -1750,31 +1750,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>24</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="3">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="22">
@@ -1782,31 +1782,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="3">
+        <v>23</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="3">
-        <v>12</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="23">
@@ -1814,13 +1814,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -1829,16 +1829,16 @@
         <v>12</v>
       </c>
       <c r="G23" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24">
@@ -1846,13 +1846,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1861,16 +1861,16 @@
         <v>10</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="25">
@@ -1878,13 +1878,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="D25" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>28</v>
@@ -1893,13 +1893,13 @@
         <v>9</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>105</v>
@@ -1910,7 +1910,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>58</v>
@@ -1925,13 +1925,13 @@
         <v>8</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>105</v>
@@ -1987,7 +1987,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2002,22 +2002,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
@@ -2040,7 +2040,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2052,7 +2052,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2075,7 +2075,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2087,7 +2087,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -2110,7 +2110,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2122,7 +2122,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -2145,7 +2145,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2157,7 +2157,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -2180,7 +2180,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2192,7 +2192,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -2215,7 +2215,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2227,7 +2227,7 @@
         <v>62</v>
       </c>
       <c r="K7" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
@@ -2250,7 +2250,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2262,7 +2262,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -2285,7 +2285,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2297,7 +2297,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -2320,7 +2320,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2332,7 +2332,7 @@
         <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -2355,7 +2355,7 @@
         <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2367,7 +2367,7 @@
         <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -2390,7 +2390,7 @@
         <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2402,7 +2402,7 @@
         <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -2425,7 +2425,7 @@
         <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2437,7 +2437,7 @@
         <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -2460,7 +2460,7 @@
         <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2472,7 +2472,7 @@
         <v>117</v>
       </c>
       <c r="K14" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -2495,7 +2495,7 @@
         <v>121</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2507,7 +2507,7 @@
         <v>62</v>
       </c>
       <c r="K15" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
@@ -2530,7 +2530,7 @@
         <v>125</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
@@ -2542,7 +2542,7 @@
         <v>127</v>
       </c>
       <c r="K16" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
@@ -2565,7 +2565,7 @@
         <v>129</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2577,7 +2577,7 @@
         <v>62</v>
       </c>
       <c r="K17" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -2588,19 +2588,19 @@
         <v>132</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>133</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
@@ -2612,7 +2612,7 @@
         <v>135</v>
       </c>
       <c r="K18" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2623,7 +2623,7 @@
         <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>27</v>
@@ -2632,33 +2632,33 @@
         <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="K19" s="3">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
@@ -2667,103 +2667,103 @@
         <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="K20" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>24</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="3">
-        <v>23</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="K21" s="3">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="3">
+        <v>23</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="3">
-        <v>12</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="K22" s="3">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -2772,33 +2772,33 @@
         <v>12</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="K23" s="3">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>27</v>
@@ -2807,33 +2807,33 @@
         <v>10</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="K24" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>28</v>
@@ -2842,27 +2842,27 @@
         <v>9</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>105</v>
       </c>
       <c r="K25" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>58</v>
@@ -2877,33 +2877,33 @@
         <v>8</v>
       </c>
       <c r="F26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>105</v>
       </c>
       <c r="K26" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -2912,33 +2912,33 @@
         <v>8</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="K27" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>26</v>
@@ -2947,33 +2947,33 @@
         <v>4</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I28" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="K28" s="3">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -2982,33 +2982,33 @@
         <v>4</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="3" t="s">
+      <c r="J29" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="C30" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>28</v>
@@ -3017,33 +3017,33 @@
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>71</v>
       </c>
       <c r="K30" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3052,33 +3052,33 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I31" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="K31" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
@@ -3088,30 +3088,30 @@
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="K32" s="3">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3121,19 +3121,19 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="K33" s="3">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3178,11 +3178,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3201,10 +3201,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3212,25 +3212,25 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>190</v>
+        <v>131</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>191</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>193</v>
+        <v>134</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>194</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -3251,40 +3251,40 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B3" s="3">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="B3" s="3">
-        <v>18</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="B4" s="3">
         <v>14</v>
@@ -3295,18 +3295,18 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="B5" s="3">
         <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>159</v>
+        <v>222</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>224</v>
@@ -3453,7 +3453,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>245</v>
@@ -3475,7 +3475,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>247</v>
@@ -3558,7 +3558,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>254</v>
